--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.90/Food use (.1010)/U.S.A.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.90/Food use (.1010)/U.S.A.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\9개년_품목별 국가별 수출입실적\대두유\1507.90\식품용(.1010)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\15개년_품목별 국가별 수출입실적\대두유\1507.90\식품용(.1010)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11640" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11640"/>
   </bookViews>
   <sheets>
     <sheet name="2010년" sheetId="11" r:id="rId1"/>
@@ -3179,12 +3179,20 @@
       </c>
       <c r="B9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+        <v>-42286</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4344</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2382</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46630</v>
+      </c>
+      <c r="F9" s="3">
+        <v>20230</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -3257,23 +3265,23 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B3:B14)</f>
-        <v>-34817</v>
+        <v>-77103</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
-        <v>54480</v>
+        <v>58824</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="1"/>
-        <v>30077</v>
+        <v>32459</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>89297</v>
+        <v>135927</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>41700</v>
+        <v>61930</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
